--- a/samples/ss_ntmbn_ingest.xlsx
+++ b/samples/ss_ntmbn_ingest.xlsx
@@ -632,31 +632,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -703,15 +693,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -727,7 +713,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -774,15 +759,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -798,7 +779,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -827,31 +807,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -880,19 +850,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -908,7 +870,6 @@
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -937,31 +898,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -990,31 +941,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1043,31 +984,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1096,35 +1027,26 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>aset milik KTT</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Milik Pelanggan</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1153,17 +1075,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>batas ke Subsistem Bekasi 1,3 - Cibinong 3</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1179,13 +1095,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1214,17 +1128,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1240,13 +1148,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1378,7 +1284,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>2</v>
       </c>
@@ -1392,8 +1297,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1410,13 +1313,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>SUTT New Tambun - Jatiwaringin (arah UP2B Jakban)</t>
@@ -1437,7 +1338,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -1451,8 +1351,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1469,13 +1367,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Tambun - Gedung Mekar</t>
@@ -1496,7 +1392,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -1510,8 +1405,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1528,13 +1421,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>SUTT Tambun - Pancoran Baru</t>
@@ -1555,7 +1446,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -1569,8 +1459,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1587,13 +1475,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>SUTT Pancoran Baru - Nusa Pancal</t>
@@ -1614,7 +1500,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -1628,8 +1513,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1646,13 +1529,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Gedung Mekar - Rejosari (arah SS Cibatu 1,2)</t>
@@ -1673,7 +1554,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -1687,8 +1567,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1705,13 +1583,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>SUTT Pancoran Baru - Tygri (aset milik KTT)</t>
@@ -1732,7 +1608,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>1</v>
       </c>
@@ -1746,8 +1621,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1764,7 +1637,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1869,8 +1741,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1909,8 +1779,6 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1994,7 +1862,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025. 2. Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani - Fajar SW, RUPTL 2025-2034, COD 2027</t>
+          <t>Jangka Pendek: 1. Pembangunan GISTET Tambun IBT 3 &amp; 4 beserta outletnya, RUPTL 2025 - 2034, COD Tahun 2025. 2. Pembangunan Outlet GITET Sukatani Penghantar 150 kV Sukatani - Fajar SW, RUPTL 2025 -2034, COD 2027</t>
         </is>
       </c>
     </row>
